--- a/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>131.88</v>
+        <v>140.67</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>96.37</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>75.24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>66.65</v>
+        <v>70.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:46</t>
+    <t xml:space="preserve">2026-10-05 16:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
